--- a/통합_테이블명세_샘플(3개시트포함).xlsx
+++ b/통합_테이블명세_샘플(3개시트포함).xlsx
@@ -498,8 +498,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F2" t="n">
-        <v>20</v>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
@@ -538,8 +540,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F3" t="n">
-        <v>50</v>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
@@ -578,8 +582,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F4" t="n">
-        <v>100</v>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
@@ -618,8 +624,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F5" t="n">
-        <v>10</v>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
@@ -658,8 +666,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F6" t="n">
-        <v>10</v>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
@@ -698,8 +708,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F7" t="n">
-        <v>20</v>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
@@ -738,8 +750,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F8" t="n">
-        <v>100</v>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
@@ -778,8 +792,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F9" t="n">
-        <v>8</v>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
@@ -818,8 +834,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F10" t="n">
-        <v>20</v>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
@@ -858,8 +876,10 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="F11" t="n">
-        <v>7</v>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
@@ -898,8 +918,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F12" t="n">
-        <v>20</v>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
@@ -938,8 +960,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F13" t="n">
-        <v>100</v>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
@@ -978,8 +1002,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F14" t="n">
-        <v>20</v>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
@@ -1018,8 +1044,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F15" t="n">
-        <v>10</v>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
@@ -1058,8 +1086,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F16" t="n">
-        <v>10</v>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
@@ -1098,8 +1128,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F17" t="n">
-        <v>12</v>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
@@ -1138,8 +1170,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F18" t="n">
-        <v>8</v>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
@@ -1178,8 +1212,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F19" t="n">
-        <v>20</v>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
@@ -1218,8 +1254,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F20" t="n">
-        <v>20</v>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
@@ -1258,8 +1296,10 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="F21" t="n">
-        <v>7</v>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
@@ -1298,8 +1338,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F22" t="n">
-        <v>20</v>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
@@ -1338,8 +1380,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F23" t="n">
-        <v>100</v>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
@@ -1378,8 +1422,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F24" t="n">
-        <v>20</v>
+      <c r="F24" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G24" t="inlineStr">
         <is>
@@ -1418,8 +1464,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F25" t="n">
-        <v>2</v>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
@@ -1458,8 +1506,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F26" t="n">
-        <v>10</v>
+      <c r="F26" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
@@ -1498,8 +1548,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F27" t="n">
-        <v>5</v>
+      <c r="F27" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
@@ -1538,8 +1590,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F28" t="n">
-        <v>1</v>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
@@ -1578,8 +1632,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F29" t="n">
-        <v>500</v>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>500</t>
+        </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
@@ -1618,8 +1674,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F30" t="n">
-        <v>20</v>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
@@ -1658,8 +1716,10 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="F31" t="n">
-        <v>7</v>
+      <c r="F31" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
@@ -1698,8 +1758,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F32" t="n">
-        <v>20</v>
+      <c r="F32" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G32" t="inlineStr">
         <is>
@@ -1738,8 +1800,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F33" t="n">
-        <v>14</v>
+      <c r="F33" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="G33" t="inlineStr">
         <is>
@@ -1778,8 +1842,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F34" t="n">
-        <v>20</v>
+      <c r="F34" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G34" t="inlineStr">
         <is>
@@ -1818,8 +1884,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F35" t="n">
-        <v>10</v>
+      <c r="F35" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G35" t="inlineStr">
         <is>
@@ -1858,8 +1926,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F36" t="n">
-        <v>10</v>
+      <c r="F36" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G36" t="inlineStr">
         <is>
@@ -1898,8 +1968,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F37" t="n">
-        <v>12</v>
+      <c r="F37" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G37" t="inlineStr">
         <is>
@@ -1938,8 +2010,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F38" t="n">
-        <v>12</v>
+      <c r="F38" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G38" t="inlineStr">
         <is>
@@ -1978,8 +2052,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F39" t="n">
-        <v>12</v>
+      <c r="F39" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G39" t="inlineStr">
         <is>
@@ -2018,8 +2094,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F40" t="n">
-        <v>20</v>
+      <c r="F40" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G40" t="inlineStr">
         <is>
@@ -2058,8 +2136,10 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="F41" t="n">
-        <v>7</v>
+      <c r="F41" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G41" t="inlineStr">
         <is>
@@ -2098,8 +2178,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F42" t="n">
-        <v>20</v>
+      <c r="F42" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G42" t="inlineStr">
         <is>
@@ -2138,8 +2220,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F43" t="n">
-        <v>20</v>
+      <c r="F43" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
@@ -2178,8 +2262,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F44" t="n">
-        <v>20</v>
+      <c r="F44" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G44" t="inlineStr">
         <is>
@@ -2218,8 +2304,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F45" t="n">
-        <v>6</v>
+      <c r="F45" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
       </c>
       <c r="G45" t="inlineStr">
         <is>
@@ -2258,8 +2346,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F46" t="n">
-        <v>12</v>
+      <c r="F46" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
@@ -2298,8 +2388,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F47" t="n">
-        <v>12</v>
+      <c r="F47" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G47" t="inlineStr">
         <is>
@@ -2338,8 +2430,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F48" t="n">
-        <v>10</v>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G48" t="inlineStr">
         <is>
@@ -2378,8 +2472,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F49" t="n">
-        <v>10</v>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G49" t="inlineStr">
         <is>
@@ -2418,8 +2514,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F50" t="n">
-        <v>20</v>
+      <c r="F50" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G50" t="inlineStr">
         <is>
@@ -2458,8 +2556,10 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="F51" t="n">
-        <v>7</v>
+      <c r="F51" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G51" t="inlineStr">
         <is>
@@ -2498,8 +2598,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F52" t="n">
-        <v>20</v>
+      <c r="F52" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
@@ -2538,8 +2640,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F53" t="n">
-        <v>20</v>
+      <c r="F53" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G53" t="inlineStr">
         <is>
@@ -2578,8 +2682,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F54" t="n">
-        <v>10</v>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G54" t="inlineStr">
         <is>
@@ -2618,8 +2724,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F55" t="n">
-        <v>10</v>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
@@ -2658,8 +2766,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F56" t="n">
-        <v>12</v>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
@@ -2698,8 +2808,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F57" t="n">
-        <v>50</v>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
@@ -2738,8 +2850,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F58" t="n">
-        <v>14</v>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
@@ -2778,8 +2892,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F59" t="n">
-        <v>12</v>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
@@ -2818,8 +2934,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F60" t="n">
-        <v>20</v>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
@@ -2858,8 +2976,10 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="F61" t="n">
-        <v>7</v>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
@@ -2898,8 +3018,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F62" t="n">
-        <v>20</v>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G62" t="inlineStr">
         <is>
@@ -2938,8 +3060,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F63" t="n">
-        <v>20</v>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G63" t="inlineStr">
         <is>
@@ -2978,8 +3102,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F64" t="n">
-        <v>10</v>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G64" t="inlineStr">
         <is>
@@ -3018,8 +3144,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F65" t="n">
-        <v>10</v>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
@@ -3058,8 +3186,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F66" t="n">
-        <v>30</v>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
@@ -3098,8 +3228,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F67" t="n">
-        <v>50</v>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
       </c>
       <c r="G67" t="inlineStr">
         <is>
@@ -3138,8 +3270,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F68" t="n">
-        <v>20</v>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
@@ -3178,8 +3312,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F69" t="n">
-        <v>200</v>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
@@ -3218,8 +3354,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F70" t="n">
-        <v>20</v>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
@@ -3258,8 +3396,10 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="F71" t="n">
-        <v>7</v>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
@@ -3298,8 +3438,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F72" t="n">
-        <v>20</v>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
@@ -3338,8 +3480,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F73" t="n">
-        <v>20</v>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G73" t="inlineStr">
         <is>
@@ -3378,8 +3522,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F74" t="n">
-        <v>100</v>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
       </c>
       <c r="G74" t="inlineStr">
         <is>
@@ -3418,8 +3564,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F75" t="n">
-        <v>10</v>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
@@ -3458,8 +3606,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F76" t="n">
-        <v>10</v>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
@@ -3498,8 +3648,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F77" t="n">
-        <v>8</v>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G77" t="inlineStr">
         <is>
@@ -3538,8 +3690,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F78" t="n">
-        <v>12</v>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
@@ -3578,8 +3732,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F79" t="n">
-        <v>8</v>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G79" t="inlineStr">
         <is>
@@ -3618,8 +3774,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F80" t="n">
-        <v>20</v>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
@@ -3658,8 +3816,10 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="F81" t="n">
-        <v>7</v>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
@@ -3698,8 +3858,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F82" t="n">
-        <v>20</v>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G82" t="inlineStr">
         <is>
@@ -3738,8 +3900,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F83" t="n">
-        <v>20</v>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G83" t="inlineStr">
         <is>
@@ -3778,8 +3942,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F84" t="n">
-        <v>20</v>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
@@ -3818,8 +3984,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F85" t="n">
-        <v>10</v>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G85" t="inlineStr">
         <is>
@@ -3858,8 +4026,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F86" t="n">
-        <v>10</v>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G86" t="inlineStr">
         <is>
@@ -3898,8 +4068,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F87" t="n">
-        <v>8</v>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
@@ -3938,8 +4110,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F88" t="n">
-        <v>8</v>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
@@ -3978,8 +4152,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F89" t="n">
-        <v>200</v>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
@@ -4018,8 +4194,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F90" t="n">
-        <v>20</v>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
@@ -4058,8 +4236,10 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="F91" t="n">
-        <v>7</v>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G91" t="inlineStr">
         <is>
@@ -4098,8 +4278,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F92" t="n">
-        <v>20</v>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
@@ -4138,8 +4320,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F93" t="n">
-        <v>20</v>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G93" t="inlineStr">
         <is>
@@ -4178,8 +4362,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F94" t="n">
-        <v>20</v>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
@@ -4218,8 +4404,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F95" t="n">
-        <v>20</v>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
@@ -4258,8 +4446,10 @@
           <t>NUMBER</t>
         </is>
       </c>
-      <c r="F96" t="n">
-        <v>2</v>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
@@ -4298,8 +4488,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F97" t="n">
-        <v>10</v>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
@@ -4338,8 +4530,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F98" t="n">
-        <v>200</v>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
@@ -4378,8 +4572,10 @@
           <t>CLOB</t>
         </is>
       </c>
-      <c r="F99" t="n">
-        <v>4000</v>
+      <c r="F99" t="inlineStr">
+        <is>
+          <t>4000</t>
+        </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
@@ -4418,8 +4614,10 @@
           <t>VARCHAR2</t>
         </is>
       </c>
-      <c r="F100" t="n">
-        <v>20</v>
+      <c r="F100" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
@@ -4458,8 +4656,10 @@
           <t>DATE</t>
         </is>
       </c>
-      <c r="F101" t="n">
-        <v>7</v>
+      <c r="F101" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
       </c>
       <c r="G101" t="inlineStr">
         <is>
@@ -4521,7 +4721,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>MEMBER_GRADE_GRP</t>
+          <t>001</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
@@ -4548,7 +4748,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>MEMBER_GRADE_GRP</t>
+          <t>001</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
@@ -4575,7 +4775,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>MEMBER_GRADE_GRP</t>
+          <t>001</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
@@ -4602,7 +4802,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>MEMBER_GRADE_GRP</t>
+          <t>001</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
@@ -4629,7 +4829,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>MEMBER_STAT_GRP</t>
+          <t>002</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
@@ -4656,7 +4856,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>MEMBER_STAT_GRP</t>
+          <t>002</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
@@ -4683,7 +4883,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>MEMBER_STAT_GRP</t>
+          <t>002</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
@@ -4710,7 +4910,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>PROD_TYPE_GRP</t>
+          <t>003</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
@@ -4737,7 +4937,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>PROD_TYPE_GRP</t>
+          <t>003</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
@@ -4764,7 +4964,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>PROD_TYPE_GRP</t>
+          <t>003</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
@@ -4791,7 +4991,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>SALE_STAT_GRP</t>
+          <t>004</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
@@ -4818,7 +5018,7 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>SALE_STAT_GRP</t>
+          <t>004</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
@@ -4845,7 +5045,7 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>SALE_STAT_GRP</t>
+          <t>004</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
@@ -4872,7 +5072,7 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>CAT_STAT_GRP</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
@@ -4899,7 +5099,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>CAT_STAT_GRP</t>
+          <t>005</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
@@ -4926,7 +5126,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>DISP_YN_GRP</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
@@ -4953,7 +5153,7 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>DISP_YN_GRP</t>
+          <t>006</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
@@ -4980,7 +5180,7 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>ORDER_STAT_GRP</t>
+          <t>007</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
@@ -5007,7 +5207,7 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>ORDER_STAT_GRP</t>
+          <t>007</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
@@ -5034,7 +5234,7 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>ORDER_STAT_GRP</t>
+          <t>007</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
@@ -5061,7 +5261,7 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>ORDER_STAT_GRP</t>
+          <t>007</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
@@ -5088,7 +5288,7 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>ORDER_STAT_GRP</t>
+          <t>007</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
@@ -5115,7 +5315,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>PAY_METHOD_GRP</t>
+          <t>008</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -5142,7 +5342,7 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>PAY_METHOD_GRP</t>
+          <t>008</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
@@ -5169,7 +5369,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>PAY_METHOD_GRP</t>
+          <t>008</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -5196,7 +5396,7 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>PAY_METHOD_GRP</t>
+          <t>008</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
@@ -5223,7 +5423,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>ITEM_STAT_GRP</t>
+          <t>009</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
@@ -5250,7 +5450,7 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>ITEM_STAT_GRP</t>
+          <t>009</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
@@ -5277,7 +5477,7 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>ITEM_STAT_GRP</t>
+          <t>009</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
@@ -5304,7 +5504,7 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>CLAIM_TYPE_GRP</t>
+          <t>010</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
@@ -5331,7 +5531,7 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>CLAIM_TYPE_GRP</t>
+          <t>010</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
@@ -5358,7 +5558,7 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>CLAIM_TYPE_GRP</t>
+          <t>010</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
@@ -5385,7 +5585,7 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>CLAIM_TYPE_GRP</t>
+          <t>010</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
@@ -5412,7 +5612,7 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>PAY_TYPE_GRP</t>
+          <t>011</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
@@ -5439,7 +5639,7 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>PAY_TYPE_GRP</t>
+          <t>011</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
@@ -5466,7 +5666,7 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>PAY_TYPE_GRP</t>
+          <t>011</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
@@ -5493,7 +5693,7 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>PAY_STAT_GRP</t>
+          <t>012</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
@@ -5520,7 +5720,7 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>PAY_STAT_GRP</t>
+          <t>012</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
@@ -5547,7 +5747,7 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>PAY_STAT_GRP</t>
+          <t>012</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
@@ -5574,7 +5774,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>PAY_STAT_GRP</t>
+          <t>012</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
@@ -5601,7 +5801,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>DELIV_STAT_GRP</t>
+          <t>013</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
@@ -5628,7 +5828,7 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>DELIV_STAT_GRP</t>
+          <t>013</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
@@ -5655,7 +5855,7 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>DELIV_STAT_GRP</t>
+          <t>013</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
@@ -5682,7 +5882,7 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>DELIV_STAT_GRP</t>
+          <t>013</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
@@ -5709,7 +5909,7 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>DELIV_CORP_GRP</t>
+          <t>014</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
@@ -5736,7 +5936,7 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>DELIV_CORP_GRP</t>
+          <t>014</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
@@ -5763,7 +5963,7 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>DELIV_CORP_GRP</t>
+          <t>014</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
@@ -5790,7 +5990,7 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>DELIV_CORP_GRP</t>
+          <t>014</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
@@ -5817,7 +6017,7 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>COUPON_TYPE_GRP</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
@@ -5844,7 +6044,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>COUPON_TYPE_GRP</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -5871,7 +6071,7 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>COUPON_TYPE_GRP</t>
+          <t>015</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
@@ -5898,7 +6098,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>COUPON_STAT_GRP</t>
+          <t>016</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -5925,7 +6125,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>COUPON_STAT_GRP</t>
+          <t>016</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -5952,7 +6152,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>COUPON_STAT_GRP</t>
+          <t>016</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -5979,7 +6179,7 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>POINT_TYPE_GRP</t>
+          <t>017</t>
         </is>
       </c>
       <c r="C56" t="inlineStr">
@@ -6006,7 +6206,7 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>POINT_TYPE_GRP</t>
+          <t>017</t>
         </is>
       </c>
       <c r="C57" t="inlineStr">
@@ -6033,7 +6233,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>POINT_TYPE_GRP</t>
+          <t>017</t>
         </is>
       </c>
       <c r="C58" t="inlineStr">
@@ -6060,7 +6260,7 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>POINT_TYPE_GRP</t>
+          <t>017</t>
         </is>
       </c>
       <c r="C59" t="inlineStr">
@@ -6087,7 +6287,7 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>POINT_STAT_GRP</t>
+          <t>018</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
@@ -6114,7 +6314,7 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>POINT_STAT_GRP</t>
+          <t>018</t>
         </is>
       </c>
       <c r="C61" t="inlineStr">
@@ -6141,7 +6341,7 @@
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>POINT_STAT_GRP</t>
+          <t>018</t>
         </is>
       </c>
       <c r="C62" t="inlineStr">
@@ -6168,7 +6368,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>RATING_SCORE_GRP</t>
+          <t>019</t>
         </is>
       </c>
       <c r="C63" t="inlineStr">
@@ -6195,7 +6395,7 @@
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>RATING_SCORE_GRP</t>
+          <t>019</t>
         </is>
       </c>
       <c r="C64" t="inlineStr">
@@ -6222,7 +6422,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>RATING_SCORE_GRP</t>
+          <t>019</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -6249,7 +6449,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>RATING_SCORE_GRP</t>
+          <t>019</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -6276,7 +6476,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>RATING_SCORE_GRP</t>
+          <t>019</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -6303,7 +6503,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>REVIEW_STAT_GRP</t>
+          <t>020</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -6330,7 +6530,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>REVIEW_STAT_GRP</t>
+          <t>020</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -6357,7 +6557,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>REVIEW_STAT_GRP</t>
+          <t>020</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
